--- a/90_temp/01_品目工程・品目構成 - コピー/kensyou/01_購買課確認用_素材不明分.xlsx
+++ b/90_temp/01_品目工程・品目構成 - コピー/kensyou/01_購買課確認用_素材不明分.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\fsrv24\TempFile\20250908_購買課依頼内容\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\90_tools\90_temp\01_品目工程・品目構成\kensyou\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9750" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9750"/>
   </bookViews>
   <sheets>
     <sheet name="購買課確認用_工程マスタ一致" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="339">
   <si>
     <t>区分コード</t>
   </si>
@@ -128,12 +128,6 @@
     <t>L-1151-201AA0280</t>
   </si>
   <si>
-    <t>TS-5509-270EA1333-1</t>
-  </si>
-  <si>
-    <t>L-TS-5509-270EA1333-1</t>
-  </si>
-  <si>
     <t>100-271EA</t>
   </si>
   <si>
@@ -359,12 +353,6 @@
     <t>MV-K-30606EA</t>
   </si>
   <si>
-    <t>K-18405B</t>
-  </si>
-  <si>
-    <t>MV-K-18405B</t>
-  </si>
-  <si>
     <t>K-18304</t>
   </si>
   <si>
@@ -395,12 +383,6 @@
     <t>MV-KD64-00102AA</t>
   </si>
   <si>
-    <t>KS64-02404EA</t>
-  </si>
-  <si>
-    <t>MC-KS64-02404-M101</t>
-  </si>
-  <si>
     <t>KS64-00515EA</t>
   </si>
   <si>
@@ -449,12 +431,6 @@
     <t>MC-KS64-00504EA</t>
   </si>
   <si>
-    <t>KS64-00504DA</t>
-  </si>
-  <si>
-    <t>MC-KS64-00504DA</t>
-  </si>
-  <si>
     <t>KS64-00504CB</t>
   </si>
   <si>
@@ -626,18 +602,9 @@
     <t>PA-162-120BA26</t>
   </si>
   <si>
-    <t>E</t>
-  </si>
-  <si>
     <t>宮木</t>
   </si>
   <si>
-    <t>DC-757UDG</t>
-  </si>
-  <si>
-    <t>AO-DC-757UDG</t>
-  </si>
-  <si>
     <t>G</t>
   </si>
   <si>
@@ -716,12 +683,6 @@
     <t>PL-EF80-00701BA</t>
   </si>
   <si>
-    <t>G-3001VH38</t>
-  </si>
-  <si>
-    <t>AO-G-3001VH38</t>
-  </si>
-  <si>
     <t>DC-7110GD21</t>
   </si>
   <si>
@@ -797,12 +758,6 @@
     <t>PA-162-307KA</t>
   </si>
   <si>
-    <t>KUT-206NA</t>
-  </si>
-  <si>
-    <t>AO-KUT-206NA</t>
-  </si>
-  <si>
     <t>1331-12A01BA38</t>
   </si>
   <si>
@@ -815,12 +770,6 @@
     <t>PA-1331-105-9CW38</t>
   </si>
   <si>
-    <t>KUT-206MA</t>
-  </si>
-  <si>
-    <t>AO-KUT-206MA</t>
-  </si>
-  <si>
     <t>KF22-002PA</t>
   </si>
   <si>
@@ -863,30 +812,6 @@
     <t>HT-KF30-00904AA</t>
   </si>
   <si>
-    <t>KUT-206SA</t>
-  </si>
-  <si>
-    <t>AO-KUT-206SA</t>
-  </si>
-  <si>
-    <t>DC-757UVB</t>
-  </si>
-  <si>
-    <t>AO-DC-757UVB</t>
-  </si>
-  <si>
-    <t>KUT-206PA</t>
-  </si>
-  <si>
-    <t>AO-KUT-206PA</t>
-  </si>
-  <si>
-    <t>KUT-206PB</t>
-  </si>
-  <si>
-    <t>AO-KUT-206PB</t>
-  </si>
-  <si>
     <t>KF22-002BA</t>
   </si>
   <si>
@@ -1089,10 +1014,6 @@
   </si>
   <si>
     <t>PA-00-757D</t>
-  </si>
-  <si>
-    <t>K-30606DC</t>
-    <phoneticPr fontId="18"/>
   </si>
   <si>
     <t>DX</t>
@@ -1128,6 +1049,9 @@
   <si>
     <t>MC-XXXXXX-XXX</t>
     <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>K-30606DC</t>
   </si>
 </sst>
 </file>
@@ -2629,7 +2553,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U151"/>
+  <dimension ref="A1:U139"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2.875" style="2" bestFit="1" customWidth="1"/>
@@ -2711,13 +2635,13 @@
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C2" t="s">
-        <v>355</v>
+        <v>91</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -2726,7 +2650,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -2761,13 +2685,13 @@
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -2776,7 +2700,7 @@
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -2811,13 +2735,13 @@
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -2826,7 +2750,7 @@
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -2861,13 +2785,13 @@
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -2876,7 +2800,7 @@
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -2911,14 +2835,14 @@
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C6" t="s">
         <v>79</v>
       </c>
-      <c r="C6" t="s">
-        <v>87</v>
-      </c>
       <c r="D6">
         <v>1</v>
       </c>
@@ -2926,7 +2850,7 @@
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -2961,13 +2885,13 @@
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -2976,7 +2900,7 @@
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -3011,13 +2935,13 @@
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -3026,7 +2950,7 @@
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -3061,10 +2985,10 @@
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
         <v>93</v>
@@ -3111,13 +3035,13 @@
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>161</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -3126,7 +3050,7 @@
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>96</v>
+        <v>162</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -3161,10 +3085,10 @@
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s">
         <v>97</v>
@@ -3211,10 +3135,10 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
         <v>99</v>
@@ -3261,10 +3185,10 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C13" t="s">
         <v>101</v>
@@ -3311,13 +3235,13 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -3326,7 +3250,7 @@
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -3361,13 +3285,13 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B15" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -3376,7 +3300,7 @@
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -3411,13 +3335,13 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C16" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -3426,7 +3350,7 @@
         <v>1</v>
       </c>
       <c r="F16" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -3461,22 +3385,22 @@
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A17" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B17" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" t="s">
+        <v>338</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17" t="s">
         <v>78</v>
-      </c>
-      <c r="B17" t="s">
-        <v>79</v>
-      </c>
-      <c r="C17" t="s">
-        <v>109</v>
-      </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-      <c r="E17">
-        <v>1</v>
-      </c>
-      <c r="F17" t="s">
-        <v>110</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -3511,13 +3435,13 @@
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B18" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C18" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -3526,7 +3450,7 @@
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -3561,13 +3485,13 @@
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A19" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B19" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C19" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -3576,7 +3500,7 @@
         <v>1</v>
       </c>
       <c r="F19" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -3611,13 +3535,13 @@
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A20" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B20" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C20" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -3626,7 +3550,7 @@
         <v>1</v>
       </c>
       <c r="F20" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -3661,13 +3585,13 @@
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A21" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C21" t="s">
-        <v>117</v>
+        <v>141</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -3676,7 +3600,7 @@
         <v>1</v>
       </c>
       <c r="F21" t="s">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -3711,13 +3635,13 @@
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A22" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C22" t="s">
-        <v>119</v>
+        <v>157</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -3726,7 +3650,7 @@
         <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>120</v>
+        <v>158</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3761,13 +3685,13 @@
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A23" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C23" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -3776,7 +3700,7 @@
         <v>1</v>
       </c>
       <c r="F23" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3811,13 +3735,13 @@
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A24" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B24" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C24" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -3826,7 +3750,7 @@
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3861,13 +3785,13 @@
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A25" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B25" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C25" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -3876,7 +3800,7 @@
         <v>1</v>
       </c>
       <c r="F25" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3911,13 +3835,13 @@
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A26" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B26" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C26" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -3926,7 +3850,7 @@
         <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3961,13 +3885,13 @@
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A27" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B27" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C27" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -3976,7 +3900,7 @@
         <v>1</v>
       </c>
       <c r="F27" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -4011,13 +3935,13 @@
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A28" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B28" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C28" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -4026,7 +3950,7 @@
         <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -4061,13 +3985,13 @@
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A29" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B29" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C29" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -4076,7 +4000,7 @@
         <v>1</v>
       </c>
       <c r="F29" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -4111,13 +4035,13 @@
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A30" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B30" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C30" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -4126,7 +4050,7 @@
         <v>1</v>
       </c>
       <c r="F30" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -4161,13 +4085,13 @@
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A31" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B31" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C31" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -4176,7 +4100,7 @@
         <v>1</v>
       </c>
       <c r="F31" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -4211,13 +4135,13 @@
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A32" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B32" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C32" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -4226,7 +4150,7 @@
         <v>1</v>
       </c>
       <c r="F32" t="s">
-        <v>140</v>
+        <v>114</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -4261,13 +4185,13 @@
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A33" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B33" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C33" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -4276,7 +4200,7 @@
         <v>1</v>
       </c>
       <c r="F33" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -4311,13 +4235,13 @@
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A34" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B34" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C34" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -4326,7 +4250,7 @@
         <v>1</v>
       </c>
       <c r="F34" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -4361,13 +4285,13 @@
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A35" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B35" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C35" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -4376,7 +4300,7 @@
         <v>1</v>
       </c>
       <c r="F35" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -4411,13 +4335,13 @@
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A36" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B36" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C36" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -4426,7 +4350,7 @@
         <v>1</v>
       </c>
       <c r="F36" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -4461,13 +4385,13 @@
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A37" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B37" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C37" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -4476,7 +4400,7 @@
         <v>1</v>
       </c>
       <c r="F37" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -4511,13 +4435,13 @@
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A38" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B38" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C38" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -4526,7 +4450,7 @@
         <v>1</v>
       </c>
       <c r="F38" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -4561,13 +4485,13 @@
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A39" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B39" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C39" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -4576,7 +4500,7 @@
         <v>1</v>
       </c>
       <c r="F39" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -4611,13 +4535,13 @@
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A40" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B40" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C40" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -4626,7 +4550,7 @@
         <v>1</v>
       </c>
       <c r="F40" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -4661,13 +4585,13 @@
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A41" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B41" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C41" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -4676,7 +4600,7 @@
         <v>1</v>
       </c>
       <c r="F41" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -4711,13 +4635,13 @@
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A42" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B42" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C42" t="s">
-        <v>159</v>
+        <v>117</v>
       </c>
       <c r="D42">
         <v>1</v>
@@ -4726,7 +4650,7 @@
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>160</v>
+        <v>118</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -4761,13 +4685,13 @@
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A43" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B43" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C43" t="s">
-        <v>161</v>
+        <v>115</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -4776,7 +4700,7 @@
         <v>1</v>
       </c>
       <c r="F43" t="s">
-        <v>162</v>
+        <v>116</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -4811,13 +4735,13 @@
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A44" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B44" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C44" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="D44">
         <v>1</v>
@@ -4826,7 +4750,7 @@
         <v>1</v>
       </c>
       <c r="F44" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -4861,13 +4785,13 @@
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A45" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B45" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C45" t="s">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="D45">
         <v>1</v>
@@ -4876,7 +4800,7 @@
         <v>1</v>
       </c>
       <c r="F45" t="s">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -4911,13 +4835,13 @@
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A46" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B46" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C46" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D46">
         <v>1</v>
@@ -4926,7 +4850,7 @@
         <v>1</v>
       </c>
       <c r="F46" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -4961,13 +4885,13 @@
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A47" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B47" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C47" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -4976,7 +4900,7 @@
         <v>1</v>
       </c>
       <c r="F47" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -5011,13 +4935,13 @@
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A48" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B48" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C48" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -5026,7 +4950,7 @@
         <v>1</v>
       </c>
       <c r="F48" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -5061,10 +4985,10 @@
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A49" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B49" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C49" t="s">
         <v>173</v>
@@ -5111,13 +5035,13 @@
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A50" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B50" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C50" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -5126,7 +5050,7 @@
         <v>1</v>
       </c>
       <c r="F50" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -5161,13 +5085,13 @@
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A51" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B51" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C51" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="D51">
         <v>1</v>
@@ -5176,7 +5100,7 @@
         <v>1</v>
       </c>
       <c r="F51" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -5211,13 +5135,13 @@
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A52" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B52" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C52" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -5226,7 +5150,7 @@
         <v>1</v>
       </c>
       <c r="F52" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -5261,13 +5185,13 @@
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A53" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B53" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C53" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -5276,7 +5200,7 @@
         <v>1</v>
       </c>
       <c r="F53" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -5311,13 +5235,13 @@
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A54" s="2" t="s">
-        <v>78</v>
+        <v>181</v>
       </c>
       <c r="B54" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C54" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -5326,7 +5250,7 @@
         <v>1</v>
       </c>
       <c r="F54" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -5361,13 +5285,13 @@
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A55" s="2" t="s">
-        <v>78</v>
+        <v>181</v>
       </c>
       <c r="B55" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C55" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -5376,7 +5300,7 @@
         <v>1</v>
       </c>
       <c r="F55" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -5411,13 +5335,13 @@
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A56" s="2" t="s">
-        <v>78</v>
+        <v>181</v>
       </c>
       <c r="B56" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C56" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -5426,7 +5350,7 @@
         <v>1</v>
       </c>
       <c r="F56" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -5461,10 +5385,10 @@
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A57" s="2" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="B57" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C57" t="s">
         <v>190</v>
@@ -5511,13 +5435,13 @@
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A58" s="2" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="B58" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C58" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -5526,7 +5450,7 @@
         <v>1</v>
       </c>
       <c r="F58" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -5561,13 +5485,13 @@
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A59" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B59" t="s">
-        <v>79</v>
+        <v>194</v>
       </c>
       <c r="C59" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -5576,7 +5500,7 @@
         <v>1</v>
       </c>
       <c r="F59" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -5611,13 +5535,13 @@
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A60" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B60" t="s">
-        <v>79</v>
+        <v>194</v>
       </c>
       <c r="C60" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="D60">
         <v>1</v>
@@ -5626,7 +5550,7 @@
         <v>1</v>
       </c>
       <c r="F60" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -5661,13 +5585,13 @@
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A61" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B61" t="s">
-        <v>79</v>
+        <v>194</v>
       </c>
       <c r="C61" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -5676,7 +5600,7 @@
         <v>1</v>
       </c>
       <c r="F61" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -5711,22 +5635,22 @@
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A62" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B62" t="s">
+        <v>194</v>
+      </c>
+      <c r="C62" t="s">
+        <v>203</v>
+      </c>
+      <c r="D62">
+        <v>1</v>
+      </c>
+      <c r="E62">
+        <v>1</v>
+      </c>
+      <c r="F62" t="s">
         <v>204</v>
-      </c>
-      <c r="B62" t="s">
-        <v>205</v>
-      </c>
-      <c r="C62" t="s">
-        <v>206</v>
-      </c>
-      <c r="D62">
-        <v>1</v>
-      </c>
-      <c r="E62">
-        <v>1</v>
-      </c>
-      <c r="F62" t="s">
-        <v>207</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -5761,13 +5685,13 @@
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A63" s="2" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="B63" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="C63" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="D63">
         <v>1</v>
@@ -5776,7 +5700,7 @@
         <v>1</v>
       </c>
       <c r="F63" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -5811,22 +5735,22 @@
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A64" s="2" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="B64" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="C64" t="s">
+        <v>209</v>
+      </c>
+      <c r="D64">
+        <v>1</v>
+      </c>
+      <c r="E64">
+        <v>1</v>
+      </c>
+      <c r="F64" t="s">
         <v>210</v>
-      </c>
-      <c r="D64">
-        <v>1</v>
-      </c>
-      <c r="E64">
-        <v>1</v>
-      </c>
-      <c r="F64" t="s">
-        <v>211</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -5861,13 +5785,13 @@
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A65" s="2" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="B65" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="C65" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -5876,7 +5800,7 @@
         <v>1</v>
       </c>
       <c r="F65" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -5911,13 +5835,13 @@
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A66" s="2" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="B66" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="C66" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -5926,7 +5850,7 @@
         <v>1</v>
       </c>
       <c r="F66" t="s">
-        <v>215</v>
+        <v>196</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -5961,13 +5885,13 @@
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A67" s="2" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="B67" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="C67" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="D67">
         <v>1</v>
@@ -5976,7 +5900,7 @@
         <v>1</v>
       </c>
       <c r="F67" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -6011,13 +5935,13 @@
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A68" s="2" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="B68" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="C68" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D68">
         <v>1</v>
@@ -6026,7 +5950,7 @@
         <v>1</v>
       </c>
       <c r="F68" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -6061,13 +5985,13 @@
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A69" s="2" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="B69" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="C69" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D69">
         <v>1</v>
@@ -6076,7 +6000,7 @@
         <v>1</v>
       </c>
       <c r="F69" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -6111,22 +6035,22 @@
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A70" s="2" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="B70" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="C70" t="s">
+        <v>221</v>
+      </c>
+      <c r="D70">
+        <v>1</v>
+      </c>
+      <c r="E70">
+        <v>1</v>
+      </c>
+      <c r="F70" t="s">
         <v>222</v>
-      </c>
-      <c r="D70">
-        <v>1</v>
-      </c>
-      <c r="E70">
-        <v>1</v>
-      </c>
-      <c r="F70" t="s">
-        <v>223</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -6161,13 +6085,13 @@
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A71" s="2" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="B71" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="C71" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="D71">
         <v>1</v>
@@ -6176,7 +6100,7 @@
         <v>1</v>
       </c>
       <c r="F71" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -6211,13 +6135,13 @@
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A72" s="2" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="B72" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="C72" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="D72">
         <v>1</v>
@@ -6226,7 +6150,7 @@
         <v>1</v>
       </c>
       <c r="F72" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -6260,14 +6184,14 @@
       </c>
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A73" s="2" t="s">
-        <v>204</v>
+      <c r="A73" s="2">
+        <v>2</v>
       </c>
       <c r="B73" t="s">
-        <v>205</v>
+        <v>21</v>
       </c>
       <c r="C73" t="s">
-        <v>228</v>
+        <v>22</v>
       </c>
       <c r="D73">
         <v>1</v>
@@ -6276,13 +6200,16 @@
         <v>1</v>
       </c>
       <c r="F73" t="s">
-        <v>229</v>
+        <v>23</v>
       </c>
       <c r="G73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H73">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I73" t="s">
+        <v>24</v>
       </c>
       <c r="J73">
         <v>0</v>
@@ -6310,14 +6237,14 @@
       </c>
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A74" s="2" t="s">
-        <v>204</v>
+      <c r="A74" s="2">
+        <v>2</v>
       </c>
       <c r="B74" t="s">
-        <v>205</v>
+        <v>21</v>
       </c>
       <c r="C74" t="s">
-        <v>230</v>
+        <v>25</v>
       </c>
       <c r="D74">
         <v>1</v>
@@ -6326,13 +6253,16 @@
         <v>1</v>
       </c>
       <c r="F74" t="s">
-        <v>231</v>
+        <v>26</v>
       </c>
       <c r="G74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H74">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I74" t="s">
+        <v>27</v>
       </c>
       <c r="J74">
         <v>0</v>
@@ -6360,14 +6290,14 @@
       </c>
     </row>
     <row r="75" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A75" s="2" t="s">
-        <v>204</v>
+      <c r="A75" s="2">
+        <v>2</v>
       </c>
       <c r="B75" t="s">
-        <v>205</v>
+        <v>21</v>
       </c>
       <c r="C75" t="s">
-        <v>232</v>
+        <v>28</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -6376,7 +6306,7 @@
         <v>1</v>
       </c>
       <c r="F75" t="s">
-        <v>233</v>
+        <v>29</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -6410,14 +6340,14 @@
       </c>
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A76" s="2" t="s">
-        <v>204</v>
+      <c r="A76" s="2">
+        <v>2</v>
       </c>
       <c r="B76" t="s">
-        <v>205</v>
+        <v>21</v>
       </c>
       <c r="C76" t="s">
-        <v>234</v>
+        <v>30</v>
       </c>
       <c r="D76">
         <v>1</v>
@@ -6426,7 +6356,7 @@
         <v>1</v>
       </c>
       <c r="F76" t="s">
-        <v>235</v>
+        <v>31</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -6467,7 +6397,7 @@
         <v>21</v>
       </c>
       <c r="C77" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -6476,16 +6406,13 @@
         <v>1</v>
       </c>
       <c r="F77" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="G77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H77">
-        <v>1</v>
-      </c>
-      <c r="I77" t="s">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J77">
         <v>0</v>
@@ -6520,7 +6447,7 @@
         <v>21</v>
       </c>
       <c r="C78" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="D78">
         <v>1</v>
@@ -6529,7 +6456,7 @@
         <v>1</v>
       </c>
       <c r="F78" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="G78">
         <v>1</v>
@@ -6538,7 +6465,7 @@
         <v>1</v>
       </c>
       <c r="I78" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="J78">
         <v>0</v>
@@ -6573,7 +6500,7 @@
         <v>21</v>
       </c>
       <c r="C79" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -6582,13 +6509,16 @@
         <v>1</v>
       </c>
       <c r="F79" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H79">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I79" t="s">
+        <v>36</v>
       </c>
       <c r="J79">
         <v>0</v>
@@ -6623,7 +6553,7 @@
         <v>21</v>
       </c>
       <c r="C80" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -6632,7 +6562,7 @@
         <v>1</v>
       </c>
       <c r="F80" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -6673,7 +6603,7 @@
         <v>21</v>
       </c>
       <c r="C81" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -6682,7 +6612,7 @@
         <v>1</v>
       </c>
       <c r="F81" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -6723,7 +6653,7 @@
         <v>21</v>
       </c>
       <c r="C82" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="D82">
         <v>1</v>
@@ -6732,7 +6662,7 @@
         <v>1</v>
       </c>
       <c r="F82" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -6773,7 +6703,7 @@
         <v>21</v>
       </c>
       <c r="C83" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -6782,16 +6712,13 @@
         <v>1</v>
       </c>
       <c r="F83" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="G83">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H83">
-        <v>1</v>
-      </c>
-      <c r="I83" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="J83">
         <v>0</v>
@@ -6876,7 +6803,7 @@
         <v>21</v>
       </c>
       <c r="C85" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D85">
         <v>1</v>
@@ -6885,7 +6812,7 @@
         <v>1</v>
       </c>
       <c r="F85" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -6926,7 +6853,7 @@
         <v>21</v>
       </c>
       <c r="C86" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="D86">
         <v>1</v>
@@ -6935,7 +6862,7 @@
         <v>1</v>
       </c>
       <c r="F86" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -6976,7 +6903,7 @@
         <v>21</v>
       </c>
       <c r="C87" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -6985,7 +6912,7 @@
         <v>1</v>
       </c>
       <c r="F87" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -7026,7 +6953,7 @@
         <v>21</v>
       </c>
       <c r="C88" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -7035,7 +6962,7 @@
         <v>1</v>
       </c>
       <c r="F88" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -7076,7 +7003,7 @@
         <v>21</v>
       </c>
       <c r="C89" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="D89">
         <v>1</v>
@@ -7085,16 +7012,13 @@
         <v>1</v>
       </c>
       <c r="F89" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="G89">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H89">
-        <v>1</v>
-      </c>
-      <c r="I89" t="s">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="J89">
         <v>0</v>
@@ -7129,7 +7053,7 @@
         <v>21</v>
       </c>
       <c r="C90" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="D90">
         <v>1</v>
@@ -7138,7 +7062,7 @@
         <v>1</v>
       </c>
       <c r="F90" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -7191,10 +7115,13 @@
         <v>55</v>
       </c>
       <c r="G91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H91">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I91" t="s">
+        <v>56</v>
       </c>
       <c r="J91">
         <v>0</v>
@@ -7229,7 +7156,7 @@
         <v>21</v>
       </c>
       <c r="C92" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -7238,16 +7165,13 @@
         <v>1</v>
       </c>
       <c r="F92" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H92">
-        <v>1</v>
-      </c>
-      <c r="I92" t="s">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="J92">
         <v>0</v>
@@ -7282,7 +7206,7 @@
         <v>21</v>
       </c>
       <c r="C93" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -7291,7 +7215,7 @@
         <v>1</v>
       </c>
       <c r="F93" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G93">
         <v>1</v>
@@ -7300,7 +7224,7 @@
         <v>1</v>
       </c>
       <c r="I93" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="J93">
         <v>0</v>
@@ -7335,25 +7259,25 @@
         <v>21</v>
       </c>
       <c r="C94" t="s">
+        <v>60</v>
+      </c>
+      <c r="D94">
+        <v>1</v>
+      </c>
+      <c r="E94">
+        <v>1</v>
+      </c>
+      <c r="F94" t="s">
+        <v>61</v>
+      </c>
+      <c r="G94">
+        <v>1</v>
+      </c>
+      <c r="H94">
+        <v>1</v>
+      </c>
+      <c r="I94" t="s">
         <v>62</v>
-      </c>
-      <c r="D94">
-        <v>1</v>
-      </c>
-      <c r="E94">
-        <v>1</v>
-      </c>
-      <c r="F94" t="s">
-        <v>63</v>
-      </c>
-      <c r="G94">
-        <v>1</v>
-      </c>
-      <c r="H94">
-        <v>1</v>
-      </c>
-      <c r="I94" t="s">
-        <v>64</v>
       </c>
       <c r="J94">
         <v>0</v>
@@ -7388,7 +7312,7 @@
         <v>21</v>
       </c>
       <c r="C95" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D95">
         <v>1</v>
@@ -7397,7 +7321,7 @@
         <v>1</v>
       </c>
       <c r="F95" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="G95">
         <v>1</v>
@@ -7406,7 +7330,7 @@
         <v>1</v>
       </c>
       <c r="I95" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="J95">
         <v>0</v>
@@ -7434,14 +7358,14 @@
       </c>
     </row>
     <row r="96" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A96" s="2">
-        <v>2</v>
+      <c r="A96" s="2" t="s">
+        <v>289</v>
       </c>
       <c r="B96" t="s">
-        <v>21</v>
+        <v>192</v>
       </c>
       <c r="C96" t="s">
-        <v>68</v>
+        <v>292</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -7450,7 +7374,7 @@
         <v>1</v>
       </c>
       <c r="F96" t="s">
-        <v>69</v>
+        <v>293</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -7484,14 +7408,14 @@
       </c>
     </row>
     <row r="97" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A97" s="2">
-        <v>2</v>
+      <c r="A97" s="2" t="s">
+        <v>289</v>
       </c>
       <c r="B97" t="s">
-        <v>21</v>
+        <v>192</v>
       </c>
       <c r="C97" t="s">
-        <v>70</v>
+        <v>290</v>
       </c>
       <c r="D97">
         <v>1</v>
@@ -7500,7 +7424,7 @@
         <v>1</v>
       </c>
       <c r="F97" t="s">
-        <v>71</v>
+        <v>291</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -7534,14 +7458,14 @@
       </c>
     </row>
     <row r="98" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A98" s="2">
-        <v>2</v>
+      <c r="A98" s="2" t="s">
+        <v>289</v>
       </c>
       <c r="B98" t="s">
-        <v>21</v>
+        <v>192</v>
       </c>
       <c r="C98" t="s">
-        <v>72</v>
+        <v>294</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -7550,7 +7474,7 @@
         <v>1</v>
       </c>
       <c r="F98" t="s">
-        <v>73</v>
+        <v>295</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -7584,14 +7508,14 @@
       </c>
     </row>
     <row r="99" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A99" s="2">
-        <v>2</v>
+      <c r="A99" s="2" t="s">
+        <v>296</v>
       </c>
       <c r="B99" t="s">
-        <v>21</v>
+        <v>297</v>
       </c>
       <c r="C99" t="s">
-        <v>74</v>
+        <v>314</v>
       </c>
       <c r="D99">
         <v>1</v>
@@ -7600,7 +7524,7 @@
         <v>1</v>
       </c>
       <c r="F99" t="s">
-        <v>75</v>
+        <v>315</v>
       </c>
       <c r="G99">
         <v>0</v>
@@ -7634,14 +7558,14 @@
       </c>
     </row>
     <row r="100" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A100" s="2">
-        <v>2</v>
+      <c r="A100" s="2" t="s">
+        <v>296</v>
       </c>
       <c r="B100" t="s">
-        <v>21</v>
+        <v>297</v>
       </c>
       <c r="C100" t="s">
-        <v>76</v>
+        <v>300</v>
       </c>
       <c r="D100">
         <v>1</v>
@@ -7650,7 +7574,7 @@
         <v>1</v>
       </c>
       <c r="F100" t="s">
-        <v>77</v>
+        <v>301</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -7685,13 +7609,13 @@
     </row>
     <row r="101" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A101" s="2" t="s">
-        <v>200</v>
+        <v>296</v>
       </c>
       <c r="B101" t="s">
-        <v>201</v>
+        <v>297</v>
       </c>
       <c r="C101" t="s">
-        <v>202</v>
+        <v>324</v>
       </c>
       <c r="D101">
         <v>1</v>
@@ -7700,7 +7624,7 @@
         <v>1</v>
       </c>
       <c r="F101" t="s">
-        <v>203</v>
+        <v>325</v>
       </c>
       <c r="G101">
         <v>0</v>
@@ -7735,13 +7659,13 @@
     </row>
     <row r="102" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A102" s="2" t="s">
-        <v>314</v>
+        <v>296</v>
       </c>
       <c r="B102" t="s">
-        <v>201</v>
+        <v>297</v>
       </c>
       <c r="C102" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="D102">
         <v>1</v>
@@ -7750,7 +7674,7 @@
         <v>1</v>
       </c>
       <c r="F102" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="G102">
         <v>0</v>
@@ -7785,13 +7709,13 @@
     </row>
     <row r="103" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A103" s="2" t="s">
-        <v>314</v>
+        <v>296</v>
       </c>
       <c r="B103" t="s">
-        <v>201</v>
+        <v>297</v>
       </c>
       <c r="C103" t="s">
-        <v>317</v>
+        <v>298</v>
       </c>
       <c r="D103">
         <v>1</v>
@@ -7800,7 +7724,7 @@
         <v>1</v>
       </c>
       <c r="F103" t="s">
-        <v>318</v>
+        <v>299</v>
       </c>
       <c r="G103">
         <v>0</v>
@@ -7835,13 +7759,13 @@
     </row>
     <row r="104" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A104" s="2" t="s">
-        <v>314</v>
+        <v>296</v>
       </c>
       <c r="B104" t="s">
-        <v>201</v>
+        <v>297</v>
       </c>
       <c r="C104" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D104">
         <v>1</v>
@@ -7850,7 +7774,7 @@
         <v>1</v>
       </c>
       <c r="F104" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G104">
         <v>0</v>
@@ -7885,13 +7809,13 @@
     </row>
     <row r="105" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A105" s="2" t="s">
-        <v>321</v>
+        <v>296</v>
       </c>
       <c r="B105" t="s">
-        <v>322</v>
+        <v>297</v>
       </c>
       <c r="C105" t="s">
-        <v>323</v>
+        <v>302</v>
       </c>
       <c r="D105">
         <v>1</v>
@@ -7900,7 +7824,7 @@
         <v>1</v>
       </c>
       <c r="F105" t="s">
-        <v>324</v>
+        <v>303</v>
       </c>
       <c r="G105">
         <v>0</v>
@@ -7935,13 +7859,13 @@
     </row>
     <row r="106" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A106" s="2" t="s">
-        <v>321</v>
+        <v>296</v>
       </c>
       <c r="B106" t="s">
-        <v>322</v>
+        <v>297</v>
       </c>
       <c r="C106" t="s">
-        <v>325</v>
+        <v>304</v>
       </c>
       <c r="D106">
         <v>1</v>
@@ -7950,7 +7874,7 @@
         <v>1</v>
       </c>
       <c r="F106" t="s">
-        <v>326</v>
+        <v>305</v>
       </c>
       <c r="G106">
         <v>0</v>
@@ -7985,13 +7909,13 @@
     </row>
     <row r="107" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A107" s="2" t="s">
-        <v>321</v>
+        <v>296</v>
       </c>
       <c r="B107" t="s">
-        <v>322</v>
+        <v>297</v>
       </c>
       <c r="C107" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="D107">
         <v>1</v>
@@ -8000,7 +7924,7 @@
         <v>1</v>
       </c>
       <c r="F107" t="s">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="G107">
         <v>0</v>
@@ -8035,13 +7959,13 @@
     </row>
     <row r="108" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A108" s="2" t="s">
-        <v>321</v>
+        <v>296</v>
       </c>
       <c r="B108" t="s">
-        <v>322</v>
+        <v>297</v>
       </c>
       <c r="C108" t="s">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="D108">
         <v>1</v>
@@ -8050,7 +7974,7 @@
         <v>1</v>
       </c>
       <c r="F108" t="s">
-        <v>330</v>
+        <v>319</v>
       </c>
       <c r="G108">
         <v>0</v>
@@ -8085,13 +8009,13 @@
     </row>
     <row r="109" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A109" s="2" t="s">
-        <v>321</v>
+        <v>296</v>
       </c>
       <c r="B109" t="s">
-        <v>322</v>
+        <v>297</v>
       </c>
       <c r="C109" t="s">
-        <v>331</v>
+        <v>306</v>
       </c>
       <c r="D109">
         <v>1</v>
@@ -8100,7 +8024,7 @@
         <v>1</v>
       </c>
       <c r="F109" t="s">
-        <v>332</v>
+        <v>307</v>
       </c>
       <c r="G109">
         <v>0</v>
@@ -8135,13 +8059,13 @@
     </row>
     <row r="110" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A110" s="2" t="s">
-        <v>321</v>
+        <v>296</v>
       </c>
       <c r="B110" t="s">
-        <v>322</v>
+        <v>297</v>
       </c>
       <c r="C110" t="s">
-        <v>333</v>
+        <v>308</v>
       </c>
       <c r="D110">
         <v>1</v>
@@ -8150,7 +8074,7 @@
         <v>1</v>
       </c>
       <c r="F110" t="s">
-        <v>334</v>
+        <v>309</v>
       </c>
       <c r="G110">
         <v>0</v>
@@ -8185,13 +8109,13 @@
     </row>
     <row r="111" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A111" s="2" t="s">
-        <v>321</v>
+        <v>296</v>
       </c>
       <c r="B111" t="s">
-        <v>322</v>
+        <v>297</v>
       </c>
       <c r="C111" t="s">
-        <v>335</v>
+        <v>310</v>
       </c>
       <c r="D111">
         <v>1</v>
@@ -8200,7 +8124,7 @@
         <v>1</v>
       </c>
       <c r="F111" t="s">
-        <v>336</v>
+        <v>311</v>
       </c>
       <c r="G111">
         <v>0</v>
@@ -8235,13 +8159,13 @@
     </row>
     <row r="112" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A112" s="2" t="s">
-        <v>321</v>
+        <v>296</v>
       </c>
       <c r="B112" t="s">
-        <v>322</v>
+        <v>297</v>
       </c>
       <c r="C112" t="s">
-        <v>337</v>
+        <v>316</v>
       </c>
       <c r="D112">
         <v>1</v>
@@ -8250,7 +8174,7 @@
         <v>1</v>
       </c>
       <c r="F112" t="s">
-        <v>338</v>
+        <v>317</v>
       </c>
       <c r="G112">
         <v>0</v>
@@ -8285,13 +8209,13 @@
     </row>
     <row r="113" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A113" s="2" t="s">
-        <v>321</v>
+        <v>296</v>
       </c>
       <c r="B113" t="s">
-        <v>322</v>
+        <v>297</v>
       </c>
       <c r="C113" t="s">
-        <v>339</v>
+        <v>326</v>
       </c>
       <c r="D113">
         <v>1</v>
@@ -8300,7 +8224,7 @@
         <v>1</v>
       </c>
       <c r="F113" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
       <c r="G113">
         <v>0</v>
@@ -8335,13 +8259,13 @@
     </row>
     <row r="114" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A114" s="2" t="s">
-        <v>321</v>
+        <v>296</v>
       </c>
       <c r="B114" t="s">
-        <v>322</v>
+        <v>297</v>
       </c>
       <c r="C114" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="D114">
         <v>1</v>
@@ -8350,7 +8274,7 @@
         <v>1</v>
       </c>
       <c r="F114" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
       <c r="G114">
         <v>0</v>
@@ -8385,13 +8309,13 @@
     </row>
     <row r="115" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A115" s="2" t="s">
-        <v>321</v>
+        <v>265</v>
       </c>
       <c r="B115" t="s">
-        <v>322</v>
+        <v>266</v>
       </c>
       <c r="C115" t="s">
-        <v>343</v>
+        <v>274</v>
       </c>
       <c r="D115">
         <v>1</v>
@@ -8400,7 +8324,7 @@
         <v>1</v>
       </c>
       <c r="F115" t="s">
-        <v>344</v>
+        <v>275</v>
       </c>
       <c r="G115">
         <v>0</v>
@@ -8435,13 +8359,13 @@
     </row>
     <row r="116" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A116" s="2" t="s">
-        <v>321</v>
+        <v>265</v>
       </c>
       <c r="B116" t="s">
-        <v>322</v>
+        <v>266</v>
       </c>
       <c r="C116" t="s">
-        <v>345</v>
+        <v>270</v>
       </c>
       <c r="D116">
         <v>1</v>
@@ -8450,7 +8374,7 @@
         <v>1</v>
       </c>
       <c r="F116" t="s">
-        <v>346</v>
+        <v>271</v>
       </c>
       <c r="G116">
         <v>0</v>
@@ -8485,13 +8409,13 @@
     </row>
     <row r="117" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A117" s="2" t="s">
-        <v>321</v>
+        <v>265</v>
       </c>
       <c r="B117" t="s">
-        <v>322</v>
+        <v>266</v>
       </c>
       <c r="C117" t="s">
-        <v>347</v>
+        <v>276</v>
       </c>
       <c r="D117">
         <v>1</v>
@@ -8500,7 +8424,7 @@
         <v>1</v>
       </c>
       <c r="F117" t="s">
-        <v>348</v>
+        <v>277</v>
       </c>
       <c r="G117">
         <v>0</v>
@@ -8535,13 +8459,13 @@
     </row>
     <row r="118" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A118" s="2" t="s">
-        <v>321</v>
+        <v>265</v>
       </c>
       <c r="B118" t="s">
-        <v>322</v>
+        <v>266</v>
       </c>
       <c r="C118" t="s">
-        <v>349</v>
+        <v>267</v>
       </c>
       <c r="D118">
         <v>1</v>
@@ -8550,13 +8474,16 @@
         <v>1</v>
       </c>
       <c r="F118" t="s">
-        <v>350</v>
+        <v>268</v>
       </c>
       <c r="G118">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H118">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I118" t="s">
+        <v>269</v>
       </c>
       <c r="J118">
         <v>0</v>
@@ -8585,13 +8512,13 @@
     </row>
     <row r="119" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A119" s="2" t="s">
-        <v>321</v>
+        <v>265</v>
       </c>
       <c r="B119" t="s">
-        <v>322</v>
+        <v>266</v>
       </c>
       <c r="C119" t="s">
-        <v>351</v>
+        <v>272</v>
       </c>
       <c r="D119">
         <v>1</v>
@@ -8600,7 +8527,7 @@
         <v>1</v>
       </c>
       <c r="F119" t="s">
-        <v>352</v>
+        <v>273</v>
       </c>
       <c r="G119">
         <v>0</v>
@@ -8635,13 +8562,13 @@
     </row>
     <row r="120" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A120" s="2" t="s">
-        <v>321</v>
+        <v>223</v>
       </c>
       <c r="B120" t="s">
-        <v>322</v>
+        <v>224</v>
       </c>
       <c r="C120" t="s">
-        <v>353</v>
+        <v>251</v>
       </c>
       <c r="D120">
         <v>1</v>
@@ -8650,13 +8577,16 @@
         <v>1</v>
       </c>
       <c r="F120" t="s">
-        <v>354</v>
+        <v>252</v>
       </c>
       <c r="G120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H120">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I120" t="s">
+        <v>227</v>
       </c>
       <c r="J120">
         <v>0</v>
@@ -8685,13 +8615,13 @@
     </row>
     <row r="121" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A121" s="2" t="s">
-        <v>290</v>
+        <v>223</v>
       </c>
       <c r="B121" t="s">
-        <v>291</v>
+        <v>224</v>
       </c>
       <c r="C121" t="s">
-        <v>292</v>
+        <v>253</v>
       </c>
       <c r="D121">
         <v>1</v>
@@ -8700,7 +8630,7 @@
         <v>1</v>
       </c>
       <c r="F121" t="s">
-        <v>293</v>
+        <v>254</v>
       </c>
       <c r="G121">
         <v>1</v>
@@ -8709,7 +8639,7 @@
         <v>1</v>
       </c>
       <c r="I121" t="s">
-        <v>294</v>
+        <v>227</v>
       </c>
       <c r="J121">
         <v>0</v>
@@ -8738,13 +8668,13 @@
     </row>
     <row r="122" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A122" s="2" t="s">
-        <v>290</v>
+        <v>223</v>
       </c>
       <c r="B122" t="s">
-        <v>291</v>
+        <v>224</v>
       </c>
       <c r="C122" t="s">
-        <v>295</v>
+        <v>228</v>
       </c>
       <c r="D122">
         <v>1</v>
@@ -8753,13 +8683,16 @@
         <v>1</v>
       </c>
       <c r="F122" t="s">
-        <v>296</v>
+        <v>229</v>
       </c>
       <c r="G122">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H122">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I122" t="s">
+        <v>230</v>
       </c>
       <c r="J122">
         <v>0</v>
@@ -8788,13 +8721,13 @@
     </row>
     <row r="123" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A123" s="2" t="s">
-        <v>290</v>
+        <v>223</v>
       </c>
       <c r="B123" t="s">
-        <v>291</v>
+        <v>224</v>
       </c>
       <c r="C123" t="s">
-        <v>297</v>
+        <v>231</v>
       </c>
       <c r="D123">
         <v>1</v>
@@ -8803,13 +8736,16 @@
         <v>1</v>
       </c>
       <c r="F123" t="s">
-        <v>298</v>
+        <v>232</v>
       </c>
       <c r="G123">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H123">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I123" t="s">
+        <v>233</v>
       </c>
       <c r="J123">
         <v>0</v>
@@ -8838,13 +8774,13 @@
     </row>
     <row r="124" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A124" s="2" t="s">
-        <v>290</v>
+        <v>223</v>
       </c>
       <c r="B124" t="s">
-        <v>291</v>
+        <v>224</v>
       </c>
       <c r="C124" t="s">
-        <v>299</v>
+        <v>234</v>
       </c>
       <c r="D124">
         <v>1</v>
@@ -8853,13 +8789,16 @@
         <v>1</v>
       </c>
       <c r="F124" t="s">
-        <v>300</v>
+        <v>235</v>
       </c>
       <c r="G124">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H124">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I124" t="s">
+        <v>236</v>
       </c>
       <c r="J124">
         <v>0</v>
@@ -8888,13 +8827,13 @@
     </row>
     <row r="125" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A125" s="2" t="s">
-        <v>290</v>
+        <v>223</v>
       </c>
       <c r="B125" t="s">
-        <v>291</v>
+        <v>224</v>
       </c>
       <c r="C125" t="s">
-        <v>301</v>
+        <v>237</v>
       </c>
       <c r="D125">
         <v>1</v>
@@ -8903,13 +8842,16 @@
         <v>1</v>
       </c>
       <c r="F125" t="s">
-        <v>302</v>
+        <v>238</v>
       </c>
       <c r="G125">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H125">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I125" t="s">
+        <v>239</v>
       </c>
       <c r="J125">
         <v>0</v>
@@ -8938,13 +8880,13 @@
     </row>
     <row r="126" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A126" s="2" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="B126" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="C126" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="D126">
         <v>1</v>
@@ -8953,7 +8895,7 @@
         <v>1</v>
       </c>
       <c r="F126" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="G126">
         <v>1</v>
@@ -8962,7 +8904,7 @@
         <v>1</v>
       </c>
       <c r="I126" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="J126">
         <v>0</v>
@@ -8991,31 +8933,28 @@
     </row>
     <row r="127" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A127" s="2" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="B127" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="C127" t="s">
+        <v>240</v>
+      </c>
+      <c r="D127">
+        <v>1</v>
+      </c>
+      <c r="E127">
+        <v>1</v>
+      </c>
+      <c r="F127" t="s">
         <v>241</v>
       </c>
-      <c r="D127">
-        <v>1</v>
-      </c>
-      <c r="E127">
-        <v>1</v>
-      </c>
-      <c r="F127" t="s">
-        <v>242</v>
-      </c>
       <c r="G127">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H127">
-        <v>1</v>
-      </c>
-      <c r="I127" t="s">
-        <v>243</v>
+        <v>0</v>
       </c>
       <c r="J127">
         <v>0</v>
@@ -9044,13 +8983,13 @@
     </row>
     <row r="128" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A128" s="2" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="B128" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="C128" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="D128">
         <v>1</v>
@@ -9059,16 +8998,13 @@
         <v>1</v>
       </c>
       <c r="F128" t="s">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="G128">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H128">
-        <v>1</v>
-      </c>
-      <c r="I128" t="s">
-        <v>246</v>
+        <v>0</v>
       </c>
       <c r="J128">
         <v>0</v>
@@ -9097,13 +9033,13 @@
     </row>
     <row r="129" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A129" s="2" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="B129" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="C129" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="D129">
         <v>1</v>
@@ -9112,16 +9048,13 @@
         <v>1</v>
       </c>
       <c r="F129" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="G129">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H129">
-        <v>1</v>
-      </c>
-      <c r="I129" t="s">
-        <v>249</v>
+        <v>0</v>
       </c>
       <c r="J129">
         <v>0</v>
@@ -9150,13 +9083,13 @@
     </row>
     <row r="130" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A130" s="2" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="B130" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="C130" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="D130">
         <v>1</v>
@@ -9165,16 +9098,13 @@
         <v>1</v>
       </c>
       <c r="F130" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="G130">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H130">
-        <v>1</v>
-      </c>
-      <c r="I130" t="s">
-        <v>252</v>
+        <v>0</v>
       </c>
       <c r="J130">
         <v>0</v>
@@ -9203,13 +9133,13 @@
     </row>
     <row r="131" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A131" s="2" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="B131" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="C131" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D131">
         <v>1</v>
@@ -9218,7 +9148,7 @@
         <v>1</v>
       </c>
       <c r="F131" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="G131">
         <v>0</v>
@@ -9253,13 +9183,13 @@
     </row>
     <row r="132" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A132" s="2" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="B132" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="C132" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="D132">
         <v>1</v>
@@ -9268,13 +9198,16 @@
         <v>1</v>
       </c>
       <c r="F132" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="G132">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H132">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I132" t="s">
+        <v>264</v>
       </c>
       <c r="J132">
         <v>0</v>
@@ -9303,28 +9236,31 @@
     </row>
     <row r="133" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A133" s="2" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="B133" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="C133" t="s">
+        <v>255</v>
+      </c>
+      <c r="D133">
+        <v>1</v>
+      </c>
+      <c r="E133">
+        <v>1</v>
+      </c>
+      <c r="F133" t="s">
+        <v>256</v>
+      </c>
+      <c r="G133">
+        <v>1</v>
+      </c>
+      <c r="H133">
+        <v>1</v>
+      </c>
+      <c r="I133" t="s">
         <v>257</v>
-      </c>
-      <c r="D133">
-        <v>1</v>
-      </c>
-      <c r="E133">
-        <v>1</v>
-      </c>
-      <c r="F133" t="s">
-        <v>258</v>
-      </c>
-      <c r="G133">
-        <v>0</v>
-      </c>
-      <c r="H133">
-        <v>0</v>
       </c>
       <c r="J133">
         <v>0</v>
@@ -9353,13 +9289,13 @@
     </row>
     <row r="134" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A134" s="2" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="B134" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="C134" t="s">
-        <v>259</v>
+        <v>225</v>
       </c>
       <c r="D134">
         <v>1</v>
@@ -9368,13 +9304,16 @@
         <v>1</v>
       </c>
       <c r="F134" t="s">
-        <v>260</v>
+        <v>226</v>
       </c>
       <c r="G134">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H134">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I134" t="s">
+        <v>227</v>
       </c>
       <c r="J134">
         <v>0</v>
@@ -9403,13 +9342,13 @@
     </row>
     <row r="135" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A135" s="2" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="B135" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="C135" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D135">
         <v>1</v>
@@ -9418,7 +9357,7 @@
         <v>1</v>
       </c>
       <c r="F135" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G135">
         <v>0</v>
@@ -9453,13 +9392,13 @@
     </row>
     <row r="136" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A136" s="2" t="s">
-        <v>236</v>
+        <v>278</v>
       </c>
       <c r="B136" t="s">
-        <v>237</v>
+        <v>279</v>
       </c>
       <c r="C136" t="s">
-        <v>263</v>
+        <v>280</v>
       </c>
       <c r="D136">
         <v>1</v>
@@ -9468,7 +9407,7 @@
         <v>1</v>
       </c>
       <c r="F136" t="s">
-        <v>264</v>
+        <v>281</v>
       </c>
       <c r="G136">
         <v>0</v>
@@ -9503,13 +9442,13 @@
     </row>
     <row r="137" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A137" s="2" t="s">
-        <v>236</v>
+        <v>278</v>
       </c>
       <c r="B137" t="s">
-        <v>237</v>
+        <v>279</v>
       </c>
       <c r="C137" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="D137">
         <v>1</v>
@@ -9518,16 +9457,13 @@
         <v>1</v>
       </c>
       <c r="F137" t="s">
-        <v>266</v>
+        <v>283</v>
       </c>
       <c r="G137">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H137">
-        <v>1</v>
-      </c>
-      <c r="I137" t="s">
-        <v>267</v>
+        <v>0</v>
       </c>
       <c r="J137">
         <v>0</v>
@@ -9556,13 +9492,13 @@
     </row>
     <row r="138" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A138" s="2" t="s">
-        <v>236</v>
+        <v>284</v>
       </c>
       <c r="B138" t="s">
-        <v>237</v>
+        <v>279</v>
       </c>
       <c r="C138" t="s">
-        <v>268</v>
+        <v>287</v>
       </c>
       <c r="D138">
         <v>1</v>
@@ -9571,16 +9507,13 @@
         <v>1</v>
       </c>
       <c r="F138" t="s">
-        <v>269</v>
+        <v>288</v>
       </c>
       <c r="G138">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H138">
-        <v>1</v>
-      </c>
-      <c r="I138" t="s">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="J138">
         <v>0</v>
@@ -9609,13 +9542,13 @@
     </row>
     <row r="139" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A139" s="2" t="s">
-        <v>236</v>
+        <v>284</v>
       </c>
       <c r="B139" t="s">
-        <v>237</v>
+        <v>279</v>
       </c>
       <c r="C139" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="D139">
         <v>1</v>
@@ -9624,16 +9557,13 @@
         <v>1</v>
       </c>
       <c r="F139" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="G139">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H139">
-        <v>1</v>
-      </c>
-      <c r="I139" t="s">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="J139">
         <v>0</v>
@@ -9657,618 +9587,12 @@
         <v>0</v>
       </c>
       <c r="T139">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A140" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="B140" t="s">
-        <v>237</v>
-      </c>
-      <c r="C140" t="s">
-        <v>272</v>
-      </c>
-      <c r="D140">
-        <v>1</v>
-      </c>
-      <c r="E140">
-        <v>1</v>
-      </c>
-      <c r="F140" t="s">
-        <v>273</v>
-      </c>
-      <c r="G140">
-        <v>1</v>
-      </c>
-      <c r="H140">
-        <v>1</v>
-      </c>
-      <c r="I140" t="s">
-        <v>274</v>
-      </c>
-      <c r="J140">
-        <v>0</v>
-      </c>
-      <c r="K140">
-        <v>0</v>
-      </c>
-      <c r="M140">
-        <v>0</v>
-      </c>
-      <c r="N140">
-        <v>0</v>
-      </c>
-      <c r="P140">
-        <v>0</v>
-      </c>
-      <c r="Q140">
-        <v>0</v>
-      </c>
-      <c r="S140">
-        <v>0</v>
-      </c>
-      <c r="T140">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A141" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="B141" t="s">
-        <v>237</v>
-      </c>
-      <c r="C141" t="s">
-        <v>275</v>
-      </c>
-      <c r="D141">
-        <v>1</v>
-      </c>
-      <c r="E141">
-        <v>1</v>
-      </c>
-      <c r="F141" t="s">
-        <v>276</v>
-      </c>
-      <c r="G141">
-        <v>0</v>
-      </c>
-      <c r="H141">
-        <v>0</v>
-      </c>
-      <c r="J141">
-        <v>0</v>
-      </c>
-      <c r="K141">
-        <v>0</v>
-      </c>
-      <c r="M141">
-        <v>0</v>
-      </c>
-      <c r="N141">
-        <v>0</v>
-      </c>
-      <c r="P141">
-        <v>0</v>
-      </c>
-      <c r="Q141">
-        <v>0</v>
-      </c>
-      <c r="S141">
-        <v>0</v>
-      </c>
-      <c r="T141">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A142" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="B142" t="s">
-        <v>237</v>
-      </c>
-      <c r="C142" t="s">
-        <v>277</v>
-      </c>
-      <c r="D142">
-        <v>1</v>
-      </c>
-      <c r="E142">
-        <v>1</v>
-      </c>
-      <c r="F142" t="s">
-        <v>278</v>
-      </c>
-      <c r="G142">
-        <v>0</v>
-      </c>
-      <c r="H142">
-        <v>0</v>
-      </c>
-      <c r="J142">
-        <v>0</v>
-      </c>
-      <c r="K142">
-        <v>0</v>
-      </c>
-      <c r="M142">
-        <v>0</v>
-      </c>
-      <c r="N142">
-        <v>0</v>
-      </c>
-      <c r="P142">
-        <v>0</v>
-      </c>
-      <c r="Q142">
-        <v>0</v>
-      </c>
-      <c r="S142">
-        <v>0</v>
-      </c>
-      <c r="T142">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A143" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="B143" t="s">
-        <v>237</v>
-      </c>
-      <c r="C143" t="s">
-        <v>279</v>
-      </c>
-      <c r="D143">
-        <v>1</v>
-      </c>
-      <c r="E143">
-        <v>1</v>
-      </c>
-      <c r="F143" t="s">
-        <v>280</v>
-      </c>
-      <c r="G143">
-        <v>0</v>
-      </c>
-      <c r="H143">
-        <v>0</v>
-      </c>
-      <c r="J143">
-        <v>0</v>
-      </c>
-      <c r="K143">
-        <v>0</v>
-      </c>
-      <c r="M143">
-        <v>0</v>
-      </c>
-      <c r="N143">
-        <v>0</v>
-      </c>
-      <c r="P143">
-        <v>0</v>
-      </c>
-      <c r="Q143">
-        <v>0</v>
-      </c>
-      <c r="S143">
-        <v>0</v>
-      </c>
-      <c r="T143">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A144" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="B144" t="s">
-        <v>237</v>
-      </c>
-      <c r="C144" t="s">
-        <v>281</v>
-      </c>
-      <c r="D144">
-        <v>1</v>
-      </c>
-      <c r="E144">
-        <v>1</v>
-      </c>
-      <c r="F144" t="s">
-        <v>282</v>
-      </c>
-      <c r="G144">
-        <v>0</v>
-      </c>
-      <c r="H144">
-        <v>0</v>
-      </c>
-      <c r="J144">
-        <v>0</v>
-      </c>
-      <c r="K144">
-        <v>0</v>
-      </c>
-      <c r="M144">
-        <v>0</v>
-      </c>
-      <c r="N144">
-        <v>0</v>
-      </c>
-      <c r="P144">
-        <v>0</v>
-      </c>
-      <c r="Q144">
-        <v>0</v>
-      </c>
-      <c r="S144">
-        <v>0</v>
-      </c>
-      <c r="T144">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A145" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="B145" t="s">
-        <v>237</v>
-      </c>
-      <c r="C145" t="s">
-        <v>283</v>
-      </c>
-      <c r="D145">
-        <v>1</v>
-      </c>
-      <c r="E145">
-        <v>1</v>
-      </c>
-      <c r="F145" t="s">
-        <v>284</v>
-      </c>
-      <c r="G145">
-        <v>0</v>
-      </c>
-      <c r="H145">
-        <v>0</v>
-      </c>
-      <c r="J145">
-        <v>0</v>
-      </c>
-      <c r="K145">
-        <v>0</v>
-      </c>
-      <c r="M145">
-        <v>0</v>
-      </c>
-      <c r="N145">
-        <v>0</v>
-      </c>
-      <c r="P145">
-        <v>0</v>
-      </c>
-      <c r="Q145">
-        <v>0</v>
-      </c>
-      <c r="S145">
-        <v>0</v>
-      </c>
-      <c r="T145">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A146" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="B146" t="s">
-        <v>237</v>
-      </c>
-      <c r="C146" t="s">
-        <v>285</v>
-      </c>
-      <c r="D146">
-        <v>1</v>
-      </c>
-      <c r="E146">
-        <v>1</v>
-      </c>
-      <c r="F146" t="s">
-        <v>286</v>
-      </c>
-      <c r="G146">
-        <v>0</v>
-      </c>
-      <c r="H146">
-        <v>0</v>
-      </c>
-      <c r="J146">
-        <v>0</v>
-      </c>
-      <c r="K146">
-        <v>0</v>
-      </c>
-      <c r="M146">
-        <v>0</v>
-      </c>
-      <c r="N146">
-        <v>0</v>
-      </c>
-      <c r="P146">
-        <v>0</v>
-      </c>
-      <c r="Q146">
-        <v>0</v>
-      </c>
-      <c r="S146">
-        <v>0</v>
-      </c>
-      <c r="T146">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A147" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="B147" t="s">
-        <v>237</v>
-      </c>
-      <c r="C147" t="s">
-        <v>287</v>
-      </c>
-      <c r="D147">
-        <v>1</v>
-      </c>
-      <c r="E147">
-        <v>1</v>
-      </c>
-      <c r="F147" t="s">
-        <v>288</v>
-      </c>
-      <c r="G147">
-        <v>1</v>
-      </c>
-      <c r="H147">
-        <v>1</v>
-      </c>
-      <c r="I147" t="s">
-        <v>289</v>
-      </c>
-      <c r="J147">
-        <v>0</v>
-      </c>
-      <c r="K147">
-        <v>0</v>
-      </c>
-      <c r="M147">
-        <v>0</v>
-      </c>
-      <c r="N147">
-        <v>0</v>
-      </c>
-      <c r="P147">
-        <v>0</v>
-      </c>
-      <c r="Q147">
-        <v>0</v>
-      </c>
-      <c r="S147">
-        <v>0</v>
-      </c>
-      <c r="T147">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A148" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="B148" t="s">
-        <v>304</v>
-      </c>
-      <c r="C148" t="s">
-        <v>305</v>
-      </c>
-      <c r="D148">
-        <v>1</v>
-      </c>
-      <c r="E148">
-        <v>1</v>
-      </c>
-      <c r="F148" t="s">
-        <v>306</v>
-      </c>
-      <c r="G148">
-        <v>0</v>
-      </c>
-      <c r="H148">
-        <v>0</v>
-      </c>
-      <c r="J148">
-        <v>0</v>
-      </c>
-      <c r="K148">
-        <v>0</v>
-      </c>
-      <c r="M148">
-        <v>0</v>
-      </c>
-      <c r="N148">
-        <v>0</v>
-      </c>
-      <c r="P148">
-        <v>0</v>
-      </c>
-      <c r="Q148">
-        <v>0</v>
-      </c>
-      <c r="S148">
-        <v>0</v>
-      </c>
-      <c r="T148">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A149" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="B149" t="s">
-        <v>304</v>
-      </c>
-      <c r="C149" t="s">
-        <v>307</v>
-      </c>
-      <c r="D149">
-        <v>1</v>
-      </c>
-      <c r="E149">
-        <v>1</v>
-      </c>
-      <c r="F149" t="s">
-        <v>308</v>
-      </c>
-      <c r="G149">
-        <v>0</v>
-      </c>
-      <c r="H149">
-        <v>0</v>
-      </c>
-      <c r="J149">
-        <v>0</v>
-      </c>
-      <c r="K149">
-        <v>0</v>
-      </c>
-      <c r="M149">
-        <v>0</v>
-      </c>
-      <c r="N149">
-        <v>0</v>
-      </c>
-      <c r="P149">
-        <v>0</v>
-      </c>
-      <c r="Q149">
-        <v>0</v>
-      </c>
-      <c r="S149">
-        <v>0</v>
-      </c>
-      <c r="T149">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A150" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="B150" t="s">
-        <v>304</v>
-      </c>
-      <c r="C150" t="s">
-        <v>310</v>
-      </c>
-      <c r="D150">
-        <v>1</v>
-      </c>
-      <c r="E150">
-        <v>1</v>
-      </c>
-      <c r="F150" t="s">
-        <v>311</v>
-      </c>
-      <c r="G150">
-        <v>0</v>
-      </c>
-      <c r="H150">
-        <v>0</v>
-      </c>
-      <c r="J150">
-        <v>0</v>
-      </c>
-      <c r="K150">
-        <v>0</v>
-      </c>
-      <c r="M150">
-        <v>0</v>
-      </c>
-      <c r="N150">
-        <v>0</v>
-      </c>
-      <c r="P150">
-        <v>0</v>
-      </c>
-      <c r="Q150">
-        <v>0</v>
-      </c>
-      <c r="S150">
-        <v>0</v>
-      </c>
-      <c r="T150">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A151" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="B151" t="s">
-        <v>304</v>
-      </c>
-      <c r="C151" t="s">
-        <v>312</v>
-      </c>
-      <c r="D151">
-        <v>1</v>
-      </c>
-      <c r="E151">
-        <v>1</v>
-      </c>
-      <c r="F151" t="s">
-        <v>313</v>
-      </c>
-      <c r="G151">
-        <v>0</v>
-      </c>
-      <c r="H151">
-        <v>0</v>
-      </c>
-      <c r="J151">
-        <v>0</v>
-      </c>
-      <c r="K151">
-        <v>0</v>
-      </c>
-      <c r="M151">
-        <v>0</v>
-      </c>
-      <c r="N151">
-        <v>0</v>
-      </c>
-      <c r="P151">
-        <v>0</v>
-      </c>
-      <c r="Q151">
-        <v>0</v>
-      </c>
-      <c r="S151">
-        <v>0</v>
-      </c>
-      <c r="T151">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:U1">
-    <sortState ref="A2:U151">
+    <sortState ref="A2:U139">
       <sortCondition ref="B1"/>
     </sortState>
   </autoFilter>
@@ -10326,13 +9650,13 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
-        <v>356</v>
+        <v>330</v>
       </c>
       <c r="B2" t="s">
-        <v>357</v>
+        <v>331</v>
       </c>
       <c r="C2" t="s">
-        <v>358</v>
+        <v>332</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -10341,7 +9665,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>359</v>
+        <v>333</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
@@ -10359,13 +9683,13 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
-        <v>356</v>
+        <v>330</v>
       </c>
       <c r="B5" t="s">
-        <v>357</v>
+        <v>331</v>
       </c>
       <c r="C5" t="s">
-        <v>358</v>
+        <v>332</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -10374,7 +9698,7 @@
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>359</v>
+        <v>333</v>
       </c>
       <c r="G5" s="5">
         <v>1</v>
@@ -10383,7 +9707,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>360</v>
+        <v>334</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.15">
@@ -10403,13 +9727,13 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
-        <v>356</v>
+        <v>330</v>
       </c>
       <c r="B9" t="s">
-        <v>357</v>
+        <v>331</v>
       </c>
       <c r="C9" t="s">
-        <v>361</v>
+        <v>335</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -10418,7 +9742,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>363</v>
+        <v>337</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.15">
@@ -10433,13 +9757,13 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
-        <v>356</v>
+        <v>330</v>
       </c>
       <c r="B12" t="s">
-        <v>357</v>
+        <v>331</v>
       </c>
       <c r="C12" t="s">
-        <v>361</v>
+        <v>335</v>
       </c>
       <c r="D12" s="5">
         <v>1</v>
@@ -10448,7 +9772,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>360</v>
+        <v>334</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.15">
@@ -10463,13 +9787,13 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
-        <v>356</v>
+        <v>330</v>
       </c>
       <c r="B16" t="s">
-        <v>357</v>
+        <v>331</v>
       </c>
       <c r="C16" t="s">
-        <v>361</v>
+        <v>335</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -10478,7 +9802,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>363</v>
+        <v>337</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.15">
@@ -10493,13 +9817,13 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A19" s="2" t="s">
-        <v>356</v>
+        <v>330</v>
       </c>
       <c r="B19" t="s">
-        <v>357</v>
+        <v>331</v>
       </c>
       <c r="C19" t="s">
-        <v>361</v>
+        <v>335</v>
       </c>
       <c r="D19" s="5">
         <v>1</v>
@@ -10508,7 +9832,7 @@
         <v>1</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>363</v>
+        <v>337</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.15">
@@ -10528,13 +9852,13 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A23" s="2" t="s">
-        <v>356</v>
+        <v>330</v>
       </c>
       <c r="B23" t="s">
-        <v>357</v>
+        <v>331</v>
       </c>
       <c r="C23" t="s">
-        <v>362</v>
+        <v>336</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -10543,18 +9867,18 @@
         <v>1</v>
       </c>
       <c r="F23" t="s">
-        <v>359</v>
+        <v>333</v>
       </c>
     </row>
     <row r="26" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A26" s="7" t="s">
-        <v>356</v>
+        <v>330</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>357</v>
+        <v>331</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>362</v>
+        <v>336</v>
       </c>
       <c r="D26" s="8">
         <v>1</v>
@@ -10563,7 +9887,7 @@
         <v>1</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>359</v>
+        <v>333</v>
       </c>
     </row>
   </sheetData>
